--- a/data/dividends_info_20260318.xlsx
+++ b/data/dividends_info_20260318.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>51.75</v>
+        <v>51.45000076293945</v>
       </c>
       <c r="I2" t="n">
-        <v>1.352657004830918</v>
+        <v>1.360544197511898</v>
       </c>
       <c r="J2" t="n">
         <v>341</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>5.309999942779541</v>
+        <v>5.659999847412109</v>
       </c>
       <c r="I3" t="n">
-        <v>3.766478383337029</v>
+        <v>3.533568999855095</v>
       </c>
       <c r="J3" t="n">
         <v>243</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>30.5</v>
+        <v>31.29999923706055</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4918032786885245</v>
+        <v>0.4792332385184008</v>
       </c>
       <c r="J6" t="n">
         <v>110</v>
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>24.79999923706055</v>
+        <v>22</v>
       </c>
       <c r="I7" t="n">
-        <v>3.830645279135097</v>
+        <v>4.318181818181818</v>
       </c>
       <c r="J7" t="n">
         <v>96</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>21.10000038146973</v>
+        <v>21.14999961853027</v>
       </c>
       <c r="I8" t="n">
-        <v>0.92417059940554</v>
+        <v>0.9219858322321364</v>
       </c>
       <c r="J8" t="n">
         <v>96</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>63.31999969482422</v>
+        <v>64.26000213623047</v>
       </c>
       <c r="I9" t="n">
-        <v>0.9949463092803777</v>
+        <v>0.9803921242710314</v>
       </c>
       <c r="J9" t="n">
         <v>96</v>
@@ -899,10 +899,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>21.70000076293945</v>
+        <v>21.72999954223633</v>
       </c>
       <c r="I10" t="n">
-        <v>3.917050553526617</v>
+        <v>3.911642972416385</v>
       </c>
       <c r="J10" t="n">
         <v>96</v>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>6.579999923706055</v>
+        <v>6.449999809265137</v>
       </c>
       <c r="I11" t="n">
-        <v>2.755319180883613</v>
+        <v>2.810852796298856</v>
       </c>
       <c r="J11" t="n">
         <v>96</v>
@@ -993,10 +993,10 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>8.090000152587891</v>
+        <v>7.909999847412109</v>
       </c>
       <c r="I12" t="n">
-        <v>3.213844191545896</v>
+        <v>3.286978571624921</v>
       </c>
       <c r="J12" t="n">
         <v>96</v>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>26.95000076293945</v>
+        <v>26.70000076293945</v>
       </c>
       <c r="I13" t="n">
-        <v>4.118738287853509</v>
+        <v>4.157303251993608</v>
       </c>
       <c r="J13" t="n">
         <v>78</v>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>0.859000027179718</v>
+        <v>0.8560000061988831</v>
       </c>
       <c r="I14" t="n">
-        <v>3.492432951195177</v>
+        <v>3.504672871816521</v>
       </c>
       <c r="J14" t="n">
         <v>75</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>12.10000038146973</v>
+        <v>12.06999969482422</v>
       </c>
       <c r="I15" t="n">
-        <v>2.066115637342102</v>
+        <v>2.07125108799467</v>
       </c>
       <c r="J15" t="n">
         <v>68</v>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>3.579999923706055</v>
+        <v>3.599999904632568</v>
       </c>
       <c r="I16" t="n">
-        <v>4.189944223370775</v>
+        <v>4.166666777045641</v>
       </c>
       <c r="J16" t="n">
         <v>68</v>
@@ -1228,10 +1228,10 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>2.440999984741211</v>
+        <v>2.397000074386597</v>
       </c>
       <c r="I17" t="n">
-        <v>4.260548981979032</v>
+        <v>4.338756644661935</v>
       </c>
       <c r="J17" t="n">
         <v>61</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>8.060000419616699</v>
+        <v>8.067999839782715</v>
       </c>
       <c r="I18" t="n">
-        <v>3.598014701018975</v>
+        <v>3.594447270189958</v>
       </c>
       <c r="J18" t="n">
         <v>61</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>34.61999893188477</v>
+        <v>34.66999816894531</v>
       </c>
       <c r="I19" t="n">
-        <v>4.737146304443042</v>
+        <v>4.730314642672766</v>
       </c>
       <c r="J19" t="n">
         <v>61</v>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>33.06999969482422</v>
+        <v>33.22999954223633</v>
       </c>
       <c r="I20" t="n">
-        <v>6.047777497600097</v>
+        <v>6.018657922212547</v>
       </c>
       <c r="J20" t="n">
         <v>61</v>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>3.710000038146973</v>
+        <v>3.769999980926514</v>
       </c>
       <c r="I21" t="n">
-        <v>2.695417762042581</v>
+        <v>2.652519907319046</v>
       </c>
       <c r="J21" t="n">
         <v>61</v>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>36.95000076293945</v>
+        <v>38.29999923706055</v>
       </c>
       <c r="I22" t="n">
-        <v>0.4017861892682399</v>
+        <v>0.3876240286092341</v>
       </c>
       <c r="J22" t="n">
         <v>61</v>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>22.34000015258789</v>
+        <v>22.15999984741211</v>
       </c>
       <c r="I23" t="n">
-        <v>4.118173651370483</v>
+        <v>4.151624577323449</v>
       </c>
       <c r="J23" t="n">
         <v>61</v>
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>72.83999633789062</v>
+        <v>75.86000061035156</v>
       </c>
       <c r="I24" t="n">
-        <v>1.427787002041628</v>
+        <v>1.370946469328245</v>
       </c>
       <c r="J24" t="n">
         <v>61</v>
@@ -1604,10 +1604,10 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>51.75</v>
+        <v>51.45000076293945</v>
       </c>
       <c r="I25" t="n">
-        <v>4.251207729468599</v>
+        <v>4.275996049323108</v>
       </c>
       <c r="J25" t="n">
         <v>61</v>
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>7.217999935150146</v>
+        <v>7.239999771118164</v>
       </c>
       <c r="I26" t="n">
-        <v>11.91465790699139</v>
+        <v>11.87845341419368</v>
       </c>
       <c r="J26" t="n">
         <v>61</v>
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>11.02499961853027</v>
+        <v>11.16499996185303</v>
       </c>
       <c r="I27" t="n">
-        <v>5.079365255113295</v>
+        <v>5.01567399832806</v>
       </c>
       <c r="J27" t="n">
         <v>61</v>
@@ -1745,10 +1745,10 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>1.809999942779541</v>
+        <v>1.830000042915344</v>
       </c>
       <c r="I28" t="n">
-        <v>2.209944821245335</v>
+        <v>2.185792298467744</v>
       </c>
       <c r="J28" t="n">
         <v>61</v>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>9.100000381469727</v>
+        <v>9.020000457763672</v>
       </c>
       <c r="I29" t="n">
-        <v>3.296703158506324</v>
+        <v>3.325942181541518</v>
       </c>
       <c r="J29" t="n">
         <v>61</v>
@@ -1839,10 +1839,10 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>2.380000114440918</v>
+        <v>2.319999933242798</v>
       </c>
       <c r="I30" t="n">
-        <v>4.537814907852225</v>
+        <v>4.655172547744092</v>
       </c>
       <c r="J30" t="n">
         <v>61</v>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>63.40000152587891</v>
+        <v>63.59999847412109</v>
       </c>
       <c r="I31" t="n">
-        <v>3.249211278266515</v>
+        <v>3.238993788401137</v>
       </c>
       <c r="J31" t="n">
         <v>61</v>
@@ -1933,10 +1933,10 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>14.53999996185303</v>
+        <v>14.72000026702881</v>
       </c>
       <c r="I32" t="n">
-        <v>5.158184332652622</v>
+        <v>5.095108603224132</v>
       </c>
       <c r="J32" t="n">
         <v>61</v>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>14.72000026702881</v>
+        <v>14.92000007629395</v>
       </c>
       <c r="I33" t="n">
-        <v>2.038043441289652</v>
+        <v>2.010723850307905</v>
       </c>
       <c r="J33" t="n">
         <v>61</v>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>40.59999847412109</v>
+        <v>41</v>
       </c>
       <c r="I34" t="n">
-        <v>2.093596137797394</v>
+        <v>2.073170731707317</v>
       </c>
       <c r="J34" t="n">
         <v>61</v>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>31.6200008392334</v>
+        <v>31.42000007629395</v>
       </c>
       <c r="I35" t="n">
-        <v>2.688171971663387</v>
+        <v>2.705283252501695</v>
       </c>
       <c r="J35" t="n">
         <v>61</v>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>5.309999942779541</v>
+        <v>5.659999847412109</v>
       </c>
       <c r="I36" t="n">
-        <v>3.766478383337029</v>
+        <v>3.533568999855095</v>
       </c>
       <c r="J36" t="n">
         <v>61</v>
@@ -2168,10 +2168,10 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>21.63999938964844</v>
+        <v>22.1200008392334</v>
       </c>
       <c r="I37" t="n">
-        <v>4.621072219060935</v>
+        <v>4.520795488517063</v>
       </c>
       <c r="J37" t="n">
         <v>61</v>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>4.179999828338623</v>
+        <v>4.139999866485596</v>
       </c>
       <c r="I38" t="n">
-        <v>5.143540881087874</v>
+        <v>5.193236882456988</v>
       </c>
       <c r="J38" t="n">
         <v>61</v>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>18.8700008392334</v>
+        <v>19.14999961853027</v>
       </c>
       <c r="I39" t="n">
-        <v>4.186539294462978</v>
+        <v>4.125326452934056</v>
       </c>
       <c r="J39" t="n">
         <v>61</v>
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>4.429999828338623</v>
+        <v>4.480000019073486</v>
       </c>
       <c r="I40" t="n">
-        <v>2.099322880445295</v>
+        <v>2.075892848304796</v>
       </c>
       <c r="J40" t="n">
         <v>61</v>
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>1.904999971389771</v>
+        <v>1.889999985694885</v>
       </c>
       <c r="I41" t="n">
-        <v>3.14960634651494</v>
+        <v>3.17460319863125</v>
       </c>
       <c r="J41" t="n">
         <v>61</v>
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>5.171000003814697</v>
+        <v>5.214000225067139</v>
       </c>
       <c r="I42" t="n">
-        <v>3.674337649581032</v>
+        <v>3.644035132306759</v>
       </c>
       <c r="J42" t="n">
         <v>61</v>
@@ -2450,10 +2450,10 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>10.4399995803833</v>
+        <v>10.15999984741211</v>
       </c>
       <c r="I43" t="n">
-        <v>4.137931200799332</v>
+        <v>4.251968567795169</v>
       </c>
       <c r="J43" t="n">
         <v>61</v>
@@ -2497,10 +2497,10 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>25.29999923706055</v>
+        <v>25.21999931335449</v>
       </c>
       <c r="I44" t="n">
-        <v>1.739130487227323</v>
+        <v>1.744647152972012</v>
       </c>
       <c r="J44" t="n">
         <v>61</v>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>6.800000190734863</v>
+        <v>6.829999923706055</v>
       </c>
       <c r="I45" t="n">
-        <v>6.911764512012579</v>
+        <v>6.881405640557772</v>
       </c>
       <c r="J45" t="n">
         <v>61</v>
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>52.63999938964844</v>
+        <v>53.11999893188477</v>
       </c>
       <c r="I46" t="n">
-        <v>2.659574498922406</v>
+        <v>2.635542221669104</v>
       </c>
       <c r="J46" t="n">
         <v>61</v>
@@ -2638,10 +2638,10 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>2.828999996185303</v>
+        <v>2.821000099182129</v>
       </c>
       <c r="I47" t="n">
-        <v>10.60445388492498</v>
+        <v>10.63452638966502</v>
       </c>
       <c r="J47" t="n">
         <v>61</v>
@@ -2685,10 +2685,10 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>82.5</v>
+        <v>80.05000305175781</v>
       </c>
       <c r="I48" t="n">
-        <v>1.636363636363636</v>
+        <v>1.686445906975335</v>
       </c>
       <c r="J48" t="n">
         <v>61</v>
@@ -2732,10 +2732,10 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>3.358000040054321</v>
+        <v>3.381999969482422</v>
       </c>
       <c r="I49" t="n">
-        <v>5.062537164152326</v>
+        <v>5.026611517859258</v>
       </c>
       <c r="J49" t="n">
         <v>61</v>
@@ -2779,10 +2779,10 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>4.659999847412109</v>
+        <v>4.619999885559082</v>
       </c>
       <c r="I50" t="n">
-        <v>0.8583691268190417</v>
+        <v>0.8658008872474131</v>
       </c>
       <c r="J50" t="n">
         <v>61</v>
@@ -2826,10 +2826,10 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>28.85000038146973</v>
+        <v>29.14999961853027</v>
       </c>
       <c r="I51" t="n">
-        <v>3.639514683245592</v>
+        <v>3.602058366177572</v>
       </c>
       <c r="J51" t="n">
         <v>61</v>
@@ -2873,10 +2873,10 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>24.11000061035156</v>
+        <v>24.19000053405762</v>
       </c>
       <c r="I52" t="n">
-        <v>2.488593881421934</v>
+        <v>2.480363731928187</v>
       </c>
       <c r="J52" t="n">
         <v>61</v>
@@ -2920,10 +2920,10 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>31.39999961853027</v>
+        <v>30.89999961853027</v>
       </c>
       <c r="I53" t="n">
-        <v>1.114649695070226</v>
+        <v>1.132686098125743</v>
       </c>
       <c r="J53" t="n">
         <v>61</v>
@@ -2967,10 +2967,10 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>2.400000095367432</v>
+        <v>2.441999912261963</v>
       </c>
       <c r="I54" t="n">
-        <v>10.83333290285536</v>
+        <v>10.64701102954457</v>
       </c>
       <c r="J54" t="n">
         <v>61</v>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>14.46000003814697</v>
+        <v>14.81999969482422</v>
       </c>
       <c r="I56" t="n">
-        <v>3.457814652012091</v>
+        <v>3.373819232767066</v>
       </c>
       <c r="J56" t="n">
         <v>54</v>
@@ -3108,10 +3108,10 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>6.519999980926514</v>
+        <v>6.599999904632568</v>
       </c>
       <c r="I57" t="n">
-        <v>3.374233138705275</v>
+        <v>3.333333381498703</v>
       </c>
       <c r="J57" t="n">
         <v>54</v>
@@ -3155,10 +3155,10 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>3.569999933242798</v>
+        <v>3.519999980926514</v>
       </c>
       <c r="I58" t="n">
-        <v>4.481792800894103</v>
+        <v>4.545454570084565</v>
       </c>
       <c r="J58" t="n">
         <v>47</v>
@@ -3202,10 +3202,10 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>18.86000061035156</v>
+        <v>18.70000076293945</v>
       </c>
       <c r="I59" t="n">
-        <v>3.234358325869795</v>
+        <v>3.262031952474178</v>
       </c>
       <c r="J59" t="n">
         <v>47</v>
@@ -3249,10 +3249,10 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>8.609999656677246</v>
+        <v>8.640000343322754</v>
       </c>
       <c r="I60" t="n">
-        <v>5.929152385088609</v>
+        <v>5.908564580029553</v>
       </c>
       <c r="J60" t="n">
         <v>47</v>
@@ -3296,10 +3296,10 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>7.420000076293945</v>
+        <v>7.739999771118164</v>
       </c>
       <c r="I61" t="n">
-        <v>3.638813978757483</v>
+        <v>3.488372196178945</v>
       </c>
       <c r="J61" t="n">
         <v>47</v>
@@ -3343,10 +3343,10 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>4.619999885559082</v>
+        <v>4.650000095367432</v>
       </c>
       <c r="I62" t="n">
-        <v>7.575757763414864</v>
+        <v>7.526881566060352</v>
       </c>
       <c r="J62" t="n">
         <v>47</v>
@@ -3390,10 +3390,10 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>18.79999923706055</v>
+        <v>19</v>
       </c>
       <c r="I63" t="n">
-        <v>3.989361864023487</v>
+        <v>3.947368421052631</v>
       </c>
       <c r="J63" t="n">
         <v>47</v>
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>10.14999961853027</v>
+        <v>10.35000038146973</v>
       </c>
       <c r="I64" t="n">
-        <v>4.23645336119002</v>
+        <v>4.154589218855071</v>
       </c>
       <c r="J64" t="n">
         <v>47</v>
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>4.110000133514404</v>
+        <v>4.125</v>
       </c>
       <c r="I65" t="n">
-        <v>3.649634917937024</v>
+        <v>3.636363636363636</v>
       </c>
       <c r="J65" t="n">
         <v>47</v>
@@ -3531,10 +3531,10 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>11.52000045776367</v>
+        <v>11.72000026702881</v>
       </c>
       <c r="I66" t="n">
-        <v>1.711536390322988</v>
+        <v>1.682329313205598</v>
       </c>
       <c r="J66" t="n">
         <v>47</v>
@@ -3578,10 +3578,10 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>25.20000076293945</v>
+        <v>25.75</v>
       </c>
       <c r="I67" t="n">
-        <v>4.365079232924955</v>
+        <v>4.271844660194176</v>
       </c>
       <c r="J67" t="n">
         <v>47</v>
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>36.79999923706055</v>
+        <v>37</v>
       </c>
       <c r="I68" t="n">
-        <v>1.277173939521913</v>
+        <v>1.27027027027027</v>
       </c>
       <c r="J68" t="n">
         <v>47</v>
@@ -3672,10 +3672,10 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>21.64999961853027</v>
+        <v>22.70000076293945</v>
       </c>
       <c r="I69" t="n">
-        <v>1.247113185946232</v>
+        <v>1.189427272799075</v>
       </c>
       <c r="J69" t="n">
         <v>47</v>
@@ -3719,10 +3719,10 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>10.30000019073486</v>
+        <v>10.19999980926514</v>
       </c>
       <c r="I70" t="n">
-        <v>3.689320320030873</v>
+        <v>3.725490265743223</v>
       </c>
       <c r="J70" t="n">
         <v>47</v>
@@ -3766,10 +3766,10 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>27.54999923706055</v>
+        <v>27.70000076293945</v>
       </c>
       <c r="I71" t="n">
-        <v>1.088929249756337</v>
+        <v>1.083032461144831</v>
       </c>
       <c r="J71" t="n">
         <v>47</v>
@@ -3813,10 +3813,10 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>6.010000228881836</v>
+        <v>5.920000076293945</v>
       </c>
       <c r="I72" t="n">
-        <v>2.662229515917474</v>
+        <v>2.702702667871647</v>
       </c>
       <c r="J72" t="n">
         <v>40</v>
@@ -3860,10 +3860,10 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>2.220000028610229</v>
+        <v>2.214999914169312</v>
       </c>
       <c r="I73" t="n">
-        <v>2.927927890194284</v>
+        <v>2.93453735976224</v>
       </c>
       <c r="J73" t="n">
         <v>40</v>
@@ -3907,10 +3907,10 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>7.210000038146973</v>
+        <v>7.340000152587891</v>
       </c>
       <c r="I74" t="n">
-        <v>3.467406361682239</v>
+        <v>3.405994479603064</v>
       </c>
       <c r="J74" t="n">
         <v>40</v>
@@ -3954,10 +3954,10 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>1.299999952316284</v>
+        <v>1.279999971389771</v>
       </c>
       <c r="I75" t="n">
-        <v>5.384615582121908</v>
+        <v>5.468750122236091</v>
       </c>
       <c r="J75" t="n">
         <v>40</v>
@@ -4001,10 +4001,10 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>6.710000038146973</v>
+        <v>6.724999904632568</v>
       </c>
       <c r="I76" t="n">
-        <v>7.451564786251172</v>
+        <v>7.434944343353391</v>
       </c>
       <c r="J76" t="n">
         <v>33</v>
@@ -4048,10 +4048,10 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>17.01000022888184</v>
+        <v>17.06999969482422</v>
       </c>
       <c r="I77" t="n">
-        <v>3.821281547641274</v>
+        <v>3.807850097367524</v>
       </c>
       <c r="J77" t="n">
         <v>33</v>
@@ -4095,10 +4095,10 @@
         </is>
       </c>
       <c r="H78" t="n">
-        <v>11.65499973297119</v>
+        <v>11.89999961853027</v>
       </c>
       <c r="I78" t="n">
-        <v>4.633204739356426</v>
+        <v>4.537815271515895</v>
       </c>
       <c r="J78" t="n">
         <v>33</v>
@@ -4142,10 +4142,10 @@
         </is>
       </c>
       <c r="H79" t="n">
-        <v>6.105999946594238</v>
+        <v>6.032000064849854</v>
       </c>
       <c r="I79" t="n">
-        <v>1.63773339133056</v>
+        <v>1.657824915863776</v>
       </c>
       <c r="J79" t="n">
         <v>33</v>
@@ -4189,10 +4189,10 @@
         </is>
       </c>
       <c r="H80" t="n">
-        <v>8.340000152587891</v>
+        <v>8.520000457763672</v>
       </c>
       <c r="I80" t="n">
-        <v>1.918465192717679</v>
+        <v>1.877934171402577</v>
       </c>
       <c r="J80" t="n">
         <v>33</v>
@@ -4236,10 +4236,10 @@
         </is>
       </c>
       <c r="H81" t="n">
-        <v>292.7000122070312</v>
+        <v>290</v>
       </c>
       <c r="I81" t="n">
-        <v>1.23505290373649</v>
+        <v>1.246551724137931</v>
       </c>
       <c r="J81" t="n">
         <v>33</v>
@@ -4283,10 +4283,10 @@
         </is>
       </c>
       <c r="H82" t="n">
-        <v>25.5</v>
+        <v>26.79999923706055</v>
       </c>
       <c r="I82" t="n">
-        <v>5.333333333333334</v>
+        <v>5.074627010135566</v>
       </c>
       <c r="J82" t="n">
         <v>33</v>
@@ -4330,10 +4330,10 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>12.63000011444092</v>
+        <v>13.10999965667725</v>
       </c>
       <c r="I83" t="n">
-        <v>4.631828936653147</v>
+        <v>4.462242679785617</v>
       </c>
       <c r="J83" t="n">
         <v>33</v>
@@ -4377,10 +4377,10 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>15.98499965667725</v>
+        <v>16.11000061035156</v>
       </c>
       <c r="I84" t="n">
-        <v>3.941194954839031</v>
+        <v>3.910614376980162</v>
       </c>
       <c r="J84" t="n">
         <v>33</v>
@@ -4424,10 +4424,10 @@
         </is>
       </c>
       <c r="H85" t="n">
-        <v>98.08000183105469</v>
+        <v>100.0500030517578</v>
       </c>
       <c r="I85" t="n">
-        <v>0.91761825366834</v>
+        <v>0.899550197449182</v>
       </c>
       <c r="J85" t="n">
         <v>33</v>
@@ -4471,10 +4471,10 @@
         </is>
       </c>
       <c r="H86" t="n">
-        <v>64.13999938964844</v>
+        <v>63.88999938964844</v>
       </c>
       <c r="I86" t="n">
-        <v>2.682881222910832</v>
+        <v>2.693379271308628</v>
       </c>
       <c r="J86" t="n">
         <v>33</v>
@@ -4518,10 +4518,10 @@
         </is>
       </c>
       <c r="H87" t="n">
-        <v>22.60000038146973</v>
+        <v>23.39999961853027</v>
       </c>
       <c r="I87" t="n">
-        <v>0.6194690160925365</v>
+        <v>0.5982906080440067</v>
       </c>
       <c r="J87" t="n">
         <v>26</v>
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="H89" t="n">
-        <v>1.960000038146973</v>
+        <v>1.919999957084656</v>
       </c>
       <c r="I89" t="n">
-        <v>1.734693843789123</v>
+        <v>1.770833372914544</v>
       </c>
       <c r="J89" t="n">
         <v>12</v>
@@ -4659,10 +4659,10 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>23.34499931335449</v>
+        <v>23.06999969482422</v>
       </c>
       <c r="I90" t="n">
-        <v>1.113728882618845</v>
+        <v>1.1270047830054</v>
       </c>
       <c r="J90" t="n">
         <v>5</v>
@@ -4706,10 +4706,10 @@
         </is>
       </c>
       <c r="H91" t="n">
-        <v>29.23999977111816</v>
+        <v>29.11499977111816</v>
       </c>
       <c r="I91" t="n">
-        <v>0.3077975400290446</v>
+        <v>0.3091190132492436</v>
       </c>
       <c r="J91" t="n">
         <v>5</v>
@@ -4753,10 +4753,10 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>51.75</v>
+        <v>51.45000076293945</v>
       </c>
       <c r="I92" t="n">
-        <v>1.256038647342995</v>
+        <v>1.263362469118191</v>
       </c>
       <c r="J92" t="n">
         <v>-23</v>
@@ -6210,7 +6210,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>PININFARINA S.p.A.</t>
+          <t>Longino &amp; Cardenal S.p.A.</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6227,7 +6227,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>PLC S.p.A.</t>
+          <t>PININFARINA S.p.A.</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6397,7 +6397,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Longino &amp; Cardenal S.p.A.</t>
+          <t>PLC S.p.A.</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6431,7 +6431,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>ELSA Solutions S.p.A.</t>
+          <t>FINCANTIERI S.p.A.</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6448,7 +6448,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>ELICA S.p.A.</t>
+          <t>ATON Green Storage S.p.A.</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6465,7 +6465,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>DANIELI &amp; C. S.p.A.</t>
+          <t>BRIOSCHI SVILUPPO IMMOBILIARE S.p.A</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6475,14 +6475,14 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Confinvest F.L. S.p.A.</t>
+          <t>CREACTIVES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6492,7 +6492,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>CREACTIVES GROUP S.p.A.</t>
+          <t>BolognaFiere S.p.A.</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6526,14 +6526,14 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>BolognaFiere S.p.A.</t>
+          <t>DANIELI &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6543,14 +6543,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>BRIOSCHI SVILUPPO IMMOBILIARE S.p.A</t>
+          <t>ELICA S.p.A.</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6567,7 +6567,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>ATON Green Storage S.p.A.</t>
+          <t>ELSA Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6584,7 +6584,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>FINCANTIERI S.p.A.</t>
+          <t>Confinvest F.L. S.p.A.</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6601,7 +6601,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>Industrie Chimiche Forestali S.p.A.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -6611,14 +6611,14 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>KME Group S.p.A.</t>
+          <t>RES S.p.A.</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -6635,7 +6635,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Lindbergh S.p.A.</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -6645,14 +6645,14 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Maps S.p.A.</t>
+          <t>SOL S.p.A.</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -6669,7 +6669,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Next Geosolutions Europe S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -6686,7 +6686,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>Unipol S.p.A.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -6703,7 +6703,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>ISCC FINTECH S.p.A.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -6713,14 +6713,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>SOL S.p.A.</t>
+          <t>Edil San Felice S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -6730,14 +6730,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>Giglio.com S.p.A.</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -6754,7 +6754,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Unipol S.p.A.</t>
+          <t>GVS S.p.A.</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -6771,7 +6771,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Intred S.p.A.</t>
+          <t>Finanza.tech S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -6788,7 +6788,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>RES S.p.A.</t>
+          <t>Edil San Felice S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -6805,7 +6805,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>ENA S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -6815,14 +6815,14 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Edil San Felice S.p.A. Società Benefit</t>
+          <t>Directa SIM S.P.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -6832,14 +6832,14 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>ENA S.p.A.</t>
+          <t>Next Geosolutions Europe S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -6856,7 +6856,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Edil San Felice S.p.A. Società Benefit</t>
+          <t>Grifal S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -6866,14 +6866,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Finanza.tech S.p.A. Società Benefit</t>
+          <t>Maps S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -6890,7 +6890,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>GVS S.p.A.</t>
+          <t>Cogefeed S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -6907,7 +6907,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Giglio.com S.p.A.</t>
+          <t>KME Group S.p.A.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -6924,7 +6924,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Grifal S.p.A.</t>
+          <t>Intred S.p.A.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -6941,7 +6941,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>ISCC FINTECH S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -6951,14 +6951,14 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Industrie Chimiche Forestali S.p.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -6975,7 +6975,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Directa SIM S.P.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -6985,14 +6985,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Cogefeed S.p.A.</t>
+          <t>Alfonsino S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -7026,7 +7026,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Directa SIM S.P.A.</t>
+          <t>Lindbergh S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -7036,14 +7036,14 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Alfonsino S.p.A.</t>
+          <t>Directa SIM S.P.A.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -7077,7 +7077,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>PREMIA FINANCE S.P.A</t>
+          <t>Praexidia Industrie Strategiche S.p.A.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -7094,7 +7094,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Saccheria F.lli Franceschetti S.p.A.</t>
+          <t>Bellini Nautica S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -7111,7 +7111,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>SBE-Varvit S.p.A.</t>
+          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -7128,7 +7128,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>SBE-Varvit S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -7162,7 +7162,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -7179,7 +7179,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Bellini Nautica S.p.A.</t>
+          <t>SOSTRAVEL.COM S.p.A.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -7196,7 +7196,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Riba Mundo Tecnologia S.A.</t>
+          <t>Saccheria F.lli Franceschetti S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -7213,7 +7213,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>SOSTRAVEL.COM S.p.A.</t>
+          <t>Riba Mundo Tecnologia S.A.</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -7247,7 +7247,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>ELES S.p.A.</t>
+          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -7315,7 +7315,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>ESAUTOMOTION S.p.A.</t>
+          <t>ELES S.p.A.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -7332,7 +7332,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Energy S.p.A.</t>
+          <t>ESAUTOMOTION S.p.A.</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -7349,7 +7349,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
+          <t>Energy S.p.A.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -7468,7 +7468,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Copernico SIM S.p.A.</t>
+          <t>PREMIA FINANCE S.P.A</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -7485,7 +7485,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>PHILOGEN S.p.A.</t>
+          <t>Copernico SIM S.p.A.</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -7502,7 +7502,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Praexidia Industrie Strategiche S.p.A.</t>
+          <t>PHILOGEN S.p.A.</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -7519,7 +7519,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Telmes S.p.A.</t>
+          <t>Smart Capital S.p.A.</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -7536,7 +7536,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Yakkyo S.p.A.</t>
+          <t>Telmes S.p.A.</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -7553,7 +7553,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>YOLO GROUP S.p.A.</t>
+          <t>TradeLab S.p.A.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -7570,7 +7570,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>UCapital24 S.p.A.</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -7604,7 +7604,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>UCapital24 S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -7621,7 +7621,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>TradeLab S.p.A.</t>
+          <t>YOLO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -7638,7 +7638,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Smart Capital S.p.A.</t>
+          <t>Yakkyo S.p.A.</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -7655,7 +7655,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>MONDO TV FRANCE</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -7672,7 +7672,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Markbass S.p.A.</t>
+          <t>Datrix S.p.A.</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -7689,7 +7689,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>COFLE S.p.A.</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -7706,7 +7706,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A.B.P. Nocivelli S.p.A.</t>
+          <t>BFF Bank S.P.A.</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -7716,14 +7716,14 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Novamarine S.p.A.</t>
+          <t>Ambromobiliare S.p.A.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -7740,7 +7740,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>MIT SIM S.p.A.</t>
+          <t>ACQUAZZURRA S.p.A.</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -7757,7 +7757,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>OLIDATA S.p.A.</t>
+          <t>ABC Company S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -7774,7 +7774,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>NOTORIOUS PICTURES S.p.A.</t>
+          <t>INNOVATEC S.p.A.</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -7791,7 +7791,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Litix S.p.A.</t>
+          <t>ILPRA S.p.A.</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -7808,7 +7808,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>INNOVATEC S.p.A.</t>
+          <t>Haiki+ S.p.A.</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -7825,7 +7825,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
+          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -7842,7 +7842,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>KALEON S.P.A.</t>
+          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -7859,7 +7859,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
+          <t>KALEON S.P.A.</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -7876,7 +7876,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>ILPRA S.p.A.</t>
+          <t>doxee S.p.A.</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -7893,7 +7893,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Haiki+ S.p.A.</t>
+          <t>HEALTH ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -7910,7 +7910,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>HEALTH ITALIA S.p.A.</t>
+          <t>A.B.P. Nocivelli S.p.A.</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -7920,14 +7920,14 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Gentili Mosconi S.p.A.</t>
+          <t>AATECH S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -7944,7 +7944,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Leone Film Group S.p.A.</t>
+          <t>Otofarma S.p.A.</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -7961,7 +7961,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>EDISON S.p.A.</t>
+          <t>PLANETEL S.p.A.</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -7971,14 +7971,14 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Energy S.p.A.</t>
+          <t>PROMOTICA S.p.A.</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -7988,14 +7988,14 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>EdgeLab S.p.A.</t>
+          <t>Pasquarelli Auto S.p.A.</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -8012,7 +8012,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>PROMOTICA S.p.A.</t>
+          <t>RedFish LongTerm Capital S.p.A.</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -8022,14 +8022,14 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Annual Preliminary Results</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Pasquarelli Auto S.p.A.</t>
+          <t>Redelfi S.p.A.</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -8046,7 +8046,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>RedFish LongTerm Capital S.p.A.</t>
+          <t>T.P.S. S.p.A.</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -8063,7 +8063,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Redelfi S.p.A.</t>
+          <t>E-Globe S.p.A.</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -8080,7 +8080,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>T.P.S. S.p.A.</t>
+          <t>Gentili Mosconi S.p.A.</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -8097,7 +8097,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>doxee S.p.A.</t>
+          <t>iVision Tech S.p.A.</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -8114,7 +8114,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>iVision Tech S.p.A.</t>
+          <t>GPI S.p.A.</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -8131,7 +8131,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>EUKEDOS S.p.A.</t>
+          <t>MONDO TV FRANCE</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -8148,7 +8148,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>AATECH S.p.A. Società Benefit</t>
+          <t>Markbass S.p.A.</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -8165,7 +8165,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -8182,7 +8182,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>FRANCHETTI S.p.A.</t>
+          <t>NOTORIOUS PICTURES S.p.A.</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -8199,7 +8199,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Estrima S.p.A.</t>
+          <t>Novamarine S.p.A.</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -8216,7 +8216,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>ErreDue S.p.A.</t>
+          <t>Leone Film Group S.p.A.</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -8233,7 +8233,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -8267,7 +8267,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Emma Villas S.p.A.</t>
+          <t>MIT SIM S.p.A.</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -8284,7 +8284,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>E-Globe S.p.A.</t>
+          <t>OLIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -8301,7 +8301,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>GPI S.p.A.</t>
+          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -8318,7 +8318,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>Litix S.p.A.</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -8335,7 +8335,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Farmacosmo S.p.A.</t>
+          <t>EUKEDOS S.p.A.</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -8352,7 +8352,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>PLANETEL S.p.A.</t>
+          <t>EdgeLab S.p.A.</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -8369,7 +8369,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>ABC Company S.p.A. Società Benefit</t>
+          <t>Emma Villas S.p.A.</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -8386,7 +8386,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>ACQUAZZURRA S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -8403,7 +8403,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Ambromobiliare S.p.A.</t>
+          <t>Farmacosmo S.p.A.</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -8420,7 +8420,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Otofarma S.p.A.</t>
+          <t>FRANCHETTI S.p.A.</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -8437,7 +8437,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
+          <t>Estrima S.p.A.</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -8454,7 +8454,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>COFLE S.p.A.</t>
+          <t>Energy S.p.A.</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -8464,14 +8464,14 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>EDISON S.p.A.</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -8481,14 +8481,14 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Datrix S.p.A.</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -8505,7 +8505,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>BFF Bank S.P.A.</t>
+          <t>ErreDue S.p.A.</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -8522,7 +8522,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>WEBSOLUTE S.p.A.</t>
+          <t>UNIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -8539,7 +8539,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Vivenda Group S.p.A.</t>
+          <t>ROSETTI MARINO S.p.A.</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -8556,7 +8556,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Vantea Smart S.p.A.</t>
+          <t>Reway Group S.p.A.</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -8573,7 +8573,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Valica S.p.A.</t>
+          <t>Seri Industrial S.p.A.</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -8590,7 +8590,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>VNE S.p.A.</t>
+          <t>Società Editoriale il Fatto S.p.A.</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -8607,7 +8607,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Ferretti S.p.A.</t>
+          <t>Solid World Group S.p.A.</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -8624,7 +8624,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A.B.P. Nocivelli S.p.A.</t>
+          <t>Reti S.p.A.</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -8634,14 +8634,14 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>GEL S.p.A.</t>
+          <t>Tecno S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -8658,7 +8658,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Gismondi 1754 S.p.A.</t>
+          <t>MARE ENGINEERING GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -8709,7 +8709,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
+          <t>NEUROSOFT</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -8726,7 +8726,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>NEUROSOFT</t>
+          <t>OPS ECOM S.p.A.</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -8743,7 +8743,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>OPS ECOM S.p.A.</t>
+          <t>OPS Retail S.p.A.</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -8760,7 +8760,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>Pozzi Milano S.p.A.</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -8777,7 +8777,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Unicredit S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -8787,14 +8787,14 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Tecno S.p.A. Società Benefit</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -8811,7 +8811,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>UNIDATA S.p.A.</t>
+          <t>Unicredit S.p.A.</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -8821,14 +8821,14 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Execus S.p.A.</t>
+          <t>Gismondi 1754 S.p.A.</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -8845,7 +8845,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Eprcomunicazione S.p.A. Società Benefit</t>
+          <t>UNIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -8855,14 +8855,14 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>DigiTouch S.p.A.</t>
+          <t>GEL S.p.A.</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -8872,14 +8872,14 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>DigiTouch S.p.A.</t>
+          <t>Valica S.p.A.</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -8896,7 +8896,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Dedem S.p.A.</t>
+          <t>Execus S.p.A.</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -8906,14 +8906,14 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Com.Tel S.p.A.</t>
+          <t>Eprcomunicazione S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -8930,7 +8930,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>CleanBnB S.p.A.</t>
+          <t>DigiTouch S.p.A.</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -8940,14 +8940,14 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>CALEFFI S.p.A.</t>
+          <t>DigiTouch S.p.A.</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -8964,7 +8964,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>BUZZI S.p.A.</t>
+          <t>Dedem S.p.A.</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -8974,14 +8974,14 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Alfio Bardolla Training Group S.p.A.</t>
+          <t>Com.Tel S.p.A.</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -8998,7 +8998,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>ROSETTI MARINO S.p.A.</t>
+          <t>A.B.P. Nocivelli S.p.A.</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -9008,14 +9008,14 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Reti S.p.A.</t>
+          <t>CALEFFI S.p.A.</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -9025,14 +9025,14 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Reway Group S.p.A.</t>
+          <t>CleanBnB S.p.A.</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -9049,7 +9049,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Società Editoriale il Fatto S.p.A.</t>
+          <t>Alfio Bardolla Training Group S.p.A.</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -9066,7 +9066,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Solid World Group S.p.A.</t>
+          <t>WEBSOLUTE S.p.A.</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -9083,7 +9083,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>UNIDATA S.p.A.</t>
+          <t>Vivenda Group S.p.A.</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -9093,14 +9093,14 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Seri Industrial S.p.A.</t>
+          <t>Vantea Smart S.p.A.</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -9117,7 +9117,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Pozzi Milano S.p.A.</t>
+          <t>BUZZI S.p.A.</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -9134,7 +9134,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>OPS Retail S.p.A.</t>
+          <t>Ferretti S.p.A.</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -9168,7 +9168,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Reti S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -9178,14 +9178,14 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Digital Value S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -9195,14 +9195,14 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>Digital Value S.p.A.</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -9212,14 +9212,14 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>Reti S.p.A.</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -9229,7 +9229,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -9304,7 +9304,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>BORGOSESIA S.p.A.</t>
+          <t>BRUNELLO CUCINELLI S.p.A.</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -9338,7 +9338,7 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Gas Plus S.p.A.</t>
+          <t>BORGOSESIA S.p.A.</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -9348,7 +9348,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -9365,14 +9365,14 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
+          <t>Gas Plus S.p.A.</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -9382,14 +9382,14 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>RT&amp;L S.P.A.</t>
+          <t>DESTINATION ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -9399,14 +9399,14 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Masi Agricola S.p.A.</t>
+          <t>Generalfinance S.p.A.</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -9423,7 +9423,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>Indel B S.p.A.</t>
+          <t>Growens S.p.A.</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -9433,14 +9433,14 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Growens S.p.A.</t>
+          <t>Indel B S.p.A.</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -9450,14 +9450,14 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Generalfinance S.p.A.</t>
+          <t>Masi Agricola S.p.A.</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -9474,7 +9474,7 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>DESTINATION ITALIA S.p.A.</t>
+          <t>RT&amp;L S.P.A.</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -9484,14 +9484,14 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Telesia S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -9501,14 +9501,14 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>BASTOGI S.p.A.</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -9518,7 +9518,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -9542,7 +9542,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>BASTOGI S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -9552,14 +9552,14 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>Triboo S.p.A.</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -9569,14 +9569,14 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Triboo S.p.A.</t>
+          <t>Telesia S.p.A.</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -9593,7 +9593,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Autostrade Meridionali S.p.A.</t>
+          <t>Ferrari N.V.</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -9610,7 +9610,7 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
+          <t>Itway S.p.A.</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -9620,14 +9620,14 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Casta Diva Group S.p.A.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -9637,14 +9637,14 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Anima Holding S.p.A.</t>
+          <t>MFE-MEDIAFOREUROPE N.V.</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -9654,14 +9654,14 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>MFE-MEDIAFOREUROPE N.V.</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -9671,14 +9671,14 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>CROWDFUNDME S.p.A.</t>
+          <t>PIAGGIO &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -9688,14 +9688,14 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Svas Biosana S.p.A.</t>
+          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -9705,14 +9705,14 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Dedem S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -9722,14 +9722,14 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -9739,14 +9739,14 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>Svas Biosana S.p.A.</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -9756,14 +9756,14 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Itway S.p.A.</t>
+          <t>Anima Holding S.p.A.</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -9773,14 +9773,14 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>Autostrade Meridionali S.p.A.</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -9797,7 +9797,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>MFE-MEDIAFOREUROPE N.V.</t>
+          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -9807,14 +9807,14 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>MFE-MEDIAFOREUROPE N.V.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -9824,14 +9824,14 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>PIAGGIO &amp; C. S.p.A.</t>
+          <t>CROWDFUNDME S.p.A.</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -9841,14 +9841,14 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Dedem S.p.A.</t>
+          <t>Casta Diva Group S.p.A.</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -9858,14 +9858,14 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
+          <t>Dedem S.p.A.</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -9875,14 +9875,14 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>Dedem S.p.A.</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -9892,14 +9892,14 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -9909,14 +9909,14 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Davide Campari-Milano N.V.</t>
+          <t>DOTSTAY S.p.A.</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -9926,14 +9926,14 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>DOTSTAY S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -9943,14 +9943,14 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>Banco BPM S.p.A.</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -9967,7 +9967,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>Banco BPM S.p.A.</t>
+          <t>Banca Generali S.p.A.</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -10001,7 +10001,7 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -10011,14 +10011,14 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -10028,14 +10028,14 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>SOLUTIONS CAPITAL MANAGEMENT SIM S.p.A.</t>
+          <t>Davide Campari-Milano N.V.</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -10052,7 +10052,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>Seri Industrial S.p.A.</t>
+          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -10062,14 +10062,14 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>Banca Generali S.p.A.</t>
+          <t>Seri Industrial S.p.A.</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -10079,14 +10079,14 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>FIDIA S.p.A</t>
+          <t>TESSELLIS S.p.A.</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -10103,7 +10103,7 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>IGD SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -10120,7 +10120,7 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>Pirelli &amp; C. S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -10130,14 +10130,14 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>PIAGGIO &amp; C. S.p.A.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -10171,7 +10171,7 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>PIAGGIO &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -10188,7 +10188,7 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>IGD SIIQ S.p.A.</t>
+          <t>Pirelli &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -10198,14 +10198,14 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>Prysmian S.p.A.</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -10215,14 +10215,14 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>Prysmian S.p.A.</t>
+          <t>SOLUTIONS CAPITAL MANAGEMENT SIM S.p.A.</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -10239,7 +10239,7 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>TESSELLIS S.p.A.</t>
+          <t>FIDIA S.p.A</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -10256,7 +10256,7 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>BEEWIZE</t>
+          <t>IGD SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -10266,14 +10266,14 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>Banca Generali S.p.A.</t>
+          <t>BEEWIZE</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -10283,14 +10283,14 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>IGD SIIQ S.p.A.</t>
+          <t>Banca Generali S.p.A.</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -10332,440 +10332,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>stock_name</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>ticker</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>detachment_date</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>payment_date</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>last_close</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>dividend</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>currency</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>ratio</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>miss_days</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>is_opportunity</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>A2A S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>IT0001233417</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2026-05-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>2.440999984741211</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.104</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>4.260548981979032</v>
-      </c>
-      <c r="I2" t="n">
-        <v>61</v>
-      </c>
-      <c r="J2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>IT0001006128</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2026-05-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>10.30000019073486</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>3.39805818950212</v>
-      </c>
-      <c r="I3" t="n">
-        <v>54</v>
-      </c>
-      <c r="J3" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Acinque S.p.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>IT0001382024</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>2026-07-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>2.140000104904175</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.08500000000000001</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>3.971962422114281</v>
-      </c>
-      <c r="I4" t="n">
-        <v>110</v>
-      </c>
-      <c r="J4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>CELLULARLINE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>IT0005244618</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>2026-05-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>2.380000114440918</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.108</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>4.537814907852225</v>
-      </c>
-      <c r="I5" t="n">
-        <v>61</v>
-      </c>
-      <c r="J5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>NL0015000K93</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>2026-06-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>26.95000076293945</v>
-      </c>
-      <c r="F6" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>4.118738287853509</v>
-      </c>
-      <c r="I6" t="n">
-        <v>78</v>
-      </c>
-      <c r="J6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>I.M.D. International Medical Devices S.p.A.</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>IT0005549255</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>2026-04-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>1.299999952316284</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>5.384615582121908</v>
-      </c>
-      <c r="I7" t="n">
-        <v>40</v>
-      </c>
-      <c r="J7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>MOLTIPLY GROUP S.p.A.</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>IT0004195308</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>2026-07-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>30.5</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>0.4918032786885245</v>
-      </c>
-      <c r="I8" t="n">
-        <v>110</v>
-      </c>
-      <c r="J8" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>REVO Insurance S.p.A.</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>IT0005513202</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>2026-05-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>21.64999961853027</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>1.247113185946232</v>
-      </c>
-      <c r="I9" t="n">
-        <v>47</v>
-      </c>
-      <c r="J9" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>IT0003153621</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>2026-06-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>8.090000152587891</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>3.213844191545896</v>
-      </c>
-      <c r="I10" t="n">
-        <v>96</v>
-      </c>
-      <c r="J10" t="b">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10776,197 +10345,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>BEEWIZE</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Banca Generali S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>DHH S.p.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Dedem S.p.A.</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>IGD SIIQ S.p.A.</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>SOLUTIONS CAPITAL MANAGEMENT SIM S.p.A.</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Somec S.p.A.</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Telesia S.p.A.</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>UNIDATA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>UNIDATA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>